--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516966</v>
+        <v>121516882</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599406</v>
+        <v>599377</v>
       </c>
       <c r="R2" t="n">
-        <v>6420301</v>
+        <v>6420328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121517008</v>
+        <v>121516898</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599395</v>
+        <v>599381</v>
       </c>
       <c r="R3" t="n">
-        <v>6420287</v>
+        <v>6420310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516831</v>
+        <v>121516848</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599418</v>
+        <v>599420</v>
       </c>
       <c r="R4" t="n">
-        <v>6420345</v>
+        <v>6420328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121517109</v>
+        <v>121516931</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,39 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599411</v>
+        <v>599381</v>
       </c>
       <c r="R5" t="n">
-        <v>6420307</v>
+        <v>6420315</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516747</v>
+        <v>121516966</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599464</v>
+        <v>599406</v>
       </c>
       <c r="R6" t="n">
-        <v>6420338</v>
+        <v>6420301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516882</v>
+        <v>121516920</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599377</v>
+        <v>599374</v>
       </c>
       <c r="R7" t="n">
-        <v>6420328</v>
+        <v>6420319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516931</v>
+        <v>121516979</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599381</v>
+        <v>599401</v>
       </c>
       <c r="R8" t="n">
-        <v>6420315</v>
+        <v>6420297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121517061</v>
+        <v>121516827</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599413</v>
+        <v>599429</v>
       </c>
       <c r="R9" t="n">
-        <v>6420284</v>
+        <v>6420340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516979</v>
+        <v>121516747</v>
       </c>
       <c r="B10" t="n">
         <v>98098</v>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599401</v>
+        <v>599464</v>
       </c>
       <c r="R10" t="n">
-        <v>6420297</v>
+        <v>6420338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516863</v>
+        <v>121516791</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599414</v>
+        <v>599443</v>
       </c>
       <c r="R11" t="n">
-        <v>6420330</v>
+        <v>6420348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516837</v>
+        <v>121516803</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599422</v>
+        <v>599436</v>
       </c>
       <c r="R12" t="n">
-        <v>6420332</v>
+        <v>6420347</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516947</v>
+        <v>121516780</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599400</v>
+        <v>599458</v>
       </c>
       <c r="R13" t="n">
-        <v>6420311</v>
+        <v>6420335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2121,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516742</v>
+        <v>121516837</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2169,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599475</v>
+        <v>599422</v>
       </c>
       <c r="R15" t="n">
-        <v>6420348</v>
+        <v>6420332</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121517033</v>
+        <v>121517008</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2280,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599403</v>
+        <v>599395</v>
       </c>
       <c r="R16" t="n">
-        <v>6420283</v>
+        <v>6420287</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516764</v>
+        <v>121516831</v>
       </c>
       <c r="B17" t="n">
         <v>98098</v>
@@ -2391,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599466</v>
+        <v>599418</v>
       </c>
       <c r="R17" t="n">
-        <v>6420338</v>
+        <v>6420345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516920</v>
+        <v>121517033</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2502,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599374</v>
+        <v>599403</v>
       </c>
       <c r="R18" t="n">
-        <v>6420319</v>
+        <v>6420283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516957</v>
+        <v>121516814</v>
       </c>
       <c r="B19" t="n">
         <v>98098</v>
@@ -2613,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599402</v>
+        <v>599427</v>
       </c>
       <c r="R19" t="n">
-        <v>6420310</v>
+        <v>6420342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516780</v>
+        <v>121517133</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2724,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599458</v>
+        <v>599443</v>
       </c>
       <c r="R20" t="n">
-        <v>6420335</v>
+        <v>6420311</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121517133</v>
+        <v>121517061</v>
       </c>
       <c r="B21" t="n">
         <v>98098</v>
@@ -2835,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599443</v>
+        <v>599413</v>
       </c>
       <c r="R21" t="n">
-        <v>6420311</v>
+        <v>6420284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516728</v>
+        <v>121517109</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,35 +2907,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2946,13 +2947,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599464</v>
+        <v>599411</v>
       </c>
       <c r="R22" t="n">
-        <v>6420340</v>
+        <v>6420307</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2991,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516848</v>
+        <v>121516863</v>
       </c>
       <c r="B23" t="n">
         <v>98098</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599420</v>
+        <v>599414</v>
       </c>
       <c r="R23" t="n">
-        <v>6420328</v>
+        <v>6420330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516791</v>
+        <v>121516742</v>
       </c>
       <c r="B24" t="n">
         <v>98098</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599443</v>
+        <v>599475</v>
       </c>
       <c r="R24" t="n">
         <v>6420348</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516827</v>
+        <v>121516947</v>
       </c>
       <c r="B25" t="n">
         <v>98098</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599429</v>
+        <v>599400</v>
       </c>
       <c r="R25" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516803</v>
+        <v>121516728</v>
       </c>
       <c r="B26" t="n">
         <v>98098</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599436</v>
+        <v>599464</v>
       </c>
       <c r="R26" t="n">
-        <v>6420347</v>
+        <v>6420340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516898</v>
+        <v>121516764</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599381</v>
+        <v>599466</v>
       </c>
       <c r="R27" t="n">
-        <v>6420310</v>
+        <v>6420338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516814</v>
+        <v>121516957</v>
       </c>
       <c r="B28" t="n">
         <v>98098</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599427</v>
+        <v>599402</v>
       </c>
       <c r="R28" t="n">
-        <v>6420342</v>
+        <v>6420310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121517033</v>
+        <v>121517133</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599403</v>
+        <v>599443</v>
       </c>
       <c r="R18" t="n">
-        <v>6420283</v>
+        <v>6420311</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516814</v>
+        <v>121517033</v>
       </c>
       <c r="B19" t="n">
         <v>98098</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599427</v>
+        <v>599403</v>
       </c>
       <c r="R19" t="n">
-        <v>6420342</v>
+        <v>6420283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121517133</v>
+        <v>121516814</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599443</v>
+        <v>599427</v>
       </c>
       <c r="R20" t="n">
-        <v>6420311</v>
+        <v>6420342</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516994</v>
+        <v>121516837</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599405</v>
+        <v>599422</v>
       </c>
       <c r="R14" t="n">
-        <v>6420283</v>
+        <v>6420332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516837</v>
+        <v>121516994</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599422</v>
+        <v>599405</v>
       </c>
       <c r="R15" t="n">
-        <v>6420332</v>
+        <v>6420283</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121517133</v>
+        <v>121517033</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599443</v>
+        <v>599403</v>
       </c>
       <c r="R18" t="n">
-        <v>6420311</v>
+        <v>6420283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121517033</v>
+        <v>121516814</v>
       </c>
       <c r="B19" t="n">
         <v>98098</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599403</v>
+        <v>599427</v>
       </c>
       <c r="R19" t="n">
-        <v>6420283</v>
+        <v>6420342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516814</v>
+        <v>121517133</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599427</v>
+        <v>599443</v>
       </c>
       <c r="R20" t="n">
-        <v>6420342</v>
+        <v>6420311</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516882</v>
+        <v>121516848</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599377</v>
+        <v>599420</v>
       </c>
       <c r="R2" t="n">
         <v>6420328</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516898</v>
+        <v>121516728</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599381</v>
+        <v>599464</v>
       </c>
       <c r="R3" t="n">
-        <v>6420310</v>
+        <v>6420340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516848</v>
+        <v>121516831</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599420</v>
+        <v>599418</v>
       </c>
       <c r="R4" t="n">
-        <v>6420328</v>
+        <v>6420345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516931</v>
+        <v>121516803</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599381</v>
+        <v>599436</v>
       </c>
       <c r="R5" t="n">
-        <v>6420315</v>
+        <v>6420347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516966</v>
+        <v>121516898</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599406</v>
+        <v>599381</v>
       </c>
       <c r="R6" t="n">
-        <v>6420301</v>
+        <v>6420310</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516920</v>
+        <v>121517109</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,35 +1242,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599374</v>
+        <v>599411</v>
       </c>
       <c r="R7" t="n">
-        <v>6420319</v>
+        <v>6420307</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516979</v>
+        <v>121516780</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599401</v>
+        <v>599458</v>
       </c>
       <c r="R8" t="n">
-        <v>6420297</v>
+        <v>6420335</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516827</v>
+        <v>121517033</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599429</v>
+        <v>599403</v>
       </c>
       <c r="R9" t="n">
-        <v>6420340</v>
+        <v>6420283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516747</v>
+        <v>121516814</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599464</v>
+        <v>599427</v>
       </c>
       <c r="R10" t="n">
-        <v>6420338</v>
+        <v>6420342</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516791</v>
+        <v>121516979</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599443</v>
+        <v>599401</v>
       </c>
       <c r="R11" t="n">
-        <v>6420348</v>
+        <v>6420297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516803</v>
+        <v>121516863</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599436</v>
+        <v>599414</v>
       </c>
       <c r="R12" t="n">
-        <v>6420347</v>
+        <v>6420330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516780</v>
+        <v>121517061</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599458</v>
+        <v>599413</v>
       </c>
       <c r="R13" t="n">
-        <v>6420335</v>
+        <v>6420284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516837</v>
+        <v>121516742</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599422</v>
+        <v>599475</v>
       </c>
       <c r="R14" t="n">
-        <v>6420332</v>
+        <v>6420348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516994</v>
+        <v>121517133</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599405</v>
+        <v>599443</v>
       </c>
       <c r="R15" t="n">
-        <v>6420283</v>
+        <v>6420311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121517008</v>
+        <v>121516957</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599395</v>
+        <v>599402</v>
       </c>
       <c r="R16" t="n">
-        <v>6420287</v>
+        <v>6420310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516831</v>
+        <v>121516947</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599418</v>
+        <v>599400</v>
       </c>
       <c r="R17" t="n">
-        <v>6420345</v>
+        <v>6420311</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121517033</v>
+        <v>121516827</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599403</v>
+        <v>599429</v>
       </c>
       <c r="R18" t="n">
-        <v>6420283</v>
+        <v>6420340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516814</v>
+        <v>121516920</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599427</v>
+        <v>599374</v>
       </c>
       <c r="R19" t="n">
-        <v>6420342</v>
+        <v>6420319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121517133</v>
+        <v>121516747</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599443</v>
+        <v>599464</v>
       </c>
       <c r="R20" t="n">
-        <v>6420311</v>
+        <v>6420338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121517061</v>
+        <v>121516791</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599413</v>
+        <v>599443</v>
       </c>
       <c r="R21" t="n">
-        <v>6420284</v>
+        <v>6420348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121517109</v>
+        <v>121516931</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>98104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,39 +2910,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2947,13 +2946,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599411</v>
+        <v>599381</v>
       </c>
       <c r="R22" t="n">
-        <v>6420307</v>
+        <v>6420315</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,6 +2990,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516863</v>
+        <v>121516837</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599414</v>
+        <v>599422</v>
       </c>
       <c r="R23" t="n">
-        <v>6420330</v>
+        <v>6420332</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516742</v>
+        <v>121516764</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599475</v>
+        <v>599466</v>
       </c>
       <c r="R24" t="n">
-        <v>6420348</v>
+        <v>6420338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516947</v>
+        <v>121516994</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599400</v>
+        <v>599405</v>
       </c>
       <c r="R25" t="n">
-        <v>6420311</v>
+        <v>6420283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516728</v>
+        <v>121516966</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599464</v>
+        <v>599406</v>
       </c>
       <c r="R26" t="n">
-        <v>6420340</v>
+        <v>6420301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516764</v>
+        <v>121517008</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599466</v>
+        <v>599395</v>
       </c>
       <c r="R27" t="n">
-        <v>6420338</v>
+        <v>6420287</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516957</v>
+        <v>121516882</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599402</v>
+        <v>599377</v>
       </c>
       <c r="R28" t="n">
-        <v>6420310</v>
+        <v>6420328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516898</v>
+        <v>121517109</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>57508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599381</v>
+        <v>599411</v>
       </c>
       <c r="R6" t="n">
-        <v>6420310</v>
+        <v>6420307</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121517109</v>
+        <v>121516898</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,39 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,13 +1281,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599411</v>
+        <v>599381</v>
       </c>
       <c r="R7" t="n">
-        <v>6420307</v>
+        <v>6420310</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516848</v>
+        <v>121516747</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599420</v>
+        <v>599464</v>
       </c>
       <c r="R2" t="n">
-        <v>6420328</v>
+        <v>6420338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516728</v>
+        <v>121516947</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599464</v>
+        <v>599400</v>
       </c>
       <c r="R3" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516831</v>
+        <v>121517033</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599418</v>
+        <v>599403</v>
       </c>
       <c r="R4" t="n">
-        <v>6420345</v>
+        <v>6420283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516803</v>
+        <v>121516882</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599436</v>
+        <v>599377</v>
       </c>
       <c r="R5" t="n">
-        <v>6420347</v>
+        <v>6420328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121517109</v>
+        <v>121517061</v>
       </c>
       <c r="B6" t="n">
-        <v>57508</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599411</v>
+        <v>599413</v>
       </c>
       <c r="R6" t="n">
-        <v>6420307</v>
+        <v>6420284</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516898</v>
+        <v>121516803</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599381</v>
+        <v>599436</v>
       </c>
       <c r="R7" t="n">
-        <v>6420310</v>
+        <v>6420347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516780</v>
+        <v>121516994</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599458</v>
+        <v>599405</v>
       </c>
       <c r="R8" t="n">
-        <v>6420335</v>
+        <v>6420283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121517033</v>
+        <v>121516827</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599403</v>
+        <v>599429</v>
       </c>
       <c r="R9" t="n">
-        <v>6420283</v>
+        <v>6420340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516814</v>
+        <v>121516791</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599427</v>
+        <v>599443</v>
       </c>
       <c r="R10" t="n">
-        <v>6420342</v>
+        <v>6420348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516979</v>
+        <v>121516837</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599401</v>
+        <v>599422</v>
       </c>
       <c r="R11" t="n">
-        <v>6420297</v>
+        <v>6420332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516863</v>
+        <v>121517008</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599414</v>
+        <v>599395</v>
       </c>
       <c r="R12" t="n">
-        <v>6420330</v>
+        <v>6420287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121517061</v>
+        <v>121516814</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599413</v>
+        <v>599427</v>
       </c>
       <c r="R13" t="n">
-        <v>6420284</v>
+        <v>6420342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516742</v>
+        <v>121517109</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,35 +2019,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2058,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599475</v>
+        <v>599411</v>
       </c>
       <c r="R14" t="n">
-        <v>6420348</v>
+        <v>6420307</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,7 +2103,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121517133</v>
+        <v>121516931</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599443</v>
+        <v>599381</v>
       </c>
       <c r="R15" t="n">
-        <v>6420311</v>
+        <v>6420315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516957</v>
+        <v>121517133</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599402</v>
+        <v>599443</v>
       </c>
       <c r="R16" t="n">
-        <v>6420310</v>
+        <v>6420311</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516947</v>
+        <v>121516920</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599400</v>
+        <v>599374</v>
       </c>
       <c r="R17" t="n">
-        <v>6420311</v>
+        <v>6420319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516827</v>
+        <v>121516898</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599429</v>
+        <v>599381</v>
       </c>
       <c r="R18" t="n">
-        <v>6420340</v>
+        <v>6420310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516920</v>
+        <v>121516780</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599374</v>
+        <v>599458</v>
       </c>
       <c r="R19" t="n">
-        <v>6420319</v>
+        <v>6420335</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516747</v>
+        <v>121516848</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599464</v>
+        <v>599420</v>
       </c>
       <c r="R20" t="n">
-        <v>6420338</v>
+        <v>6420328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516791</v>
+        <v>121516863</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599443</v>
+        <v>599414</v>
       </c>
       <c r="R21" t="n">
-        <v>6420348</v>
+        <v>6420330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516931</v>
+        <v>121516966</v>
       </c>
       <c r="B22" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599381</v>
+        <v>599406</v>
       </c>
       <c r="R22" t="n">
-        <v>6420315</v>
+        <v>6420301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516837</v>
+        <v>121516831</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599422</v>
+        <v>599418</v>
       </c>
       <c r="R23" t="n">
-        <v>6420332</v>
+        <v>6420345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
         <v>121516764</v>
       </c>
       <c r="B24" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516994</v>
+        <v>121516742</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599405</v>
+        <v>599475</v>
       </c>
       <c r="R25" t="n">
-        <v>6420283</v>
+        <v>6420348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516966</v>
+        <v>121516957</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599406</v>
+        <v>599402</v>
       </c>
       <c r="R26" t="n">
-        <v>6420301</v>
+        <v>6420310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121517008</v>
+        <v>121516728</v>
       </c>
       <c r="B27" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599395</v>
+        <v>599464</v>
       </c>
       <c r="R27" t="n">
-        <v>6420287</v>
+        <v>6420340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516882</v>
+        <v>121516979</v>
       </c>
       <c r="B28" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599377</v>
+        <v>599401</v>
       </c>
       <c r="R28" t="n">
-        <v>6420328</v>
+        <v>6420297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516747</v>
+        <v>121516931</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599464</v>
+        <v>599381</v>
       </c>
       <c r="R2" t="n">
-        <v>6420338</v>
+        <v>6420315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516947</v>
+        <v>121516848</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599400</v>
+        <v>599420</v>
       </c>
       <c r="R3" t="n">
-        <v>6420311</v>
+        <v>6420328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121517033</v>
+        <v>121516780</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599403</v>
+        <v>599458</v>
       </c>
       <c r="R4" t="n">
-        <v>6420283</v>
+        <v>6420335</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516882</v>
+        <v>121516920</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599377</v>
+        <v>599374</v>
       </c>
       <c r="R5" t="n">
-        <v>6420328</v>
+        <v>6420319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121517061</v>
+        <v>121516747</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599413</v>
+        <v>599464</v>
       </c>
       <c r="R6" t="n">
-        <v>6420284</v>
+        <v>6420338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516803</v>
+        <v>121516837</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599436</v>
+        <v>599422</v>
       </c>
       <c r="R7" t="n">
-        <v>6420347</v>
+        <v>6420332</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516994</v>
+        <v>121516957</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599405</v>
+        <v>599402</v>
       </c>
       <c r="R8" t="n">
-        <v>6420283</v>
+        <v>6420310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516827</v>
+        <v>121516898</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599429</v>
+        <v>599381</v>
       </c>
       <c r="R9" t="n">
-        <v>6420340</v>
+        <v>6420310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516791</v>
+        <v>121516803</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599443</v>
+        <v>599436</v>
       </c>
       <c r="R10" t="n">
-        <v>6420348</v>
+        <v>6420347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516837</v>
+        <v>121516831</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599422</v>
+        <v>599418</v>
       </c>
       <c r="R11" t="n">
-        <v>6420332</v>
+        <v>6420345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121517008</v>
+        <v>121516728</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599395</v>
+        <v>599464</v>
       </c>
       <c r="R12" t="n">
-        <v>6420287</v>
+        <v>6420340</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516814</v>
+        <v>121516947</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599427</v>
+        <v>599400</v>
       </c>
       <c r="R13" t="n">
-        <v>6420342</v>
+        <v>6420311</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121517109</v>
+        <v>121516814</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,39 +2019,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2059,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599411</v>
+        <v>599427</v>
       </c>
       <c r="R14" t="n">
-        <v>6420307</v>
+        <v>6420342</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,6 +2099,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516931</v>
+        <v>121517109</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,35 +2130,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599381</v>
+        <v>599411</v>
       </c>
       <c r="R15" t="n">
-        <v>6420315</v>
+        <v>6420307</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,7 +2214,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121517133</v>
+        <v>121516791</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2283,7 +2283,7 @@
         <v>599443</v>
       </c>
       <c r="R16" t="n">
-        <v>6420311</v>
+        <v>6420348</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516920</v>
+        <v>121517033</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599374</v>
+        <v>599403</v>
       </c>
       <c r="R17" t="n">
-        <v>6420319</v>
+        <v>6420283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516898</v>
+        <v>121516966</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599381</v>
+        <v>599406</v>
       </c>
       <c r="R18" t="n">
-        <v>6420310</v>
+        <v>6420301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516780</v>
+        <v>121516863</v>
       </c>
       <c r="B19" t="n">
         <v>98105</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599458</v>
+        <v>599414</v>
       </c>
       <c r="R19" t="n">
-        <v>6420335</v>
+        <v>6420330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516848</v>
+        <v>121517008</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599420</v>
+        <v>599395</v>
       </c>
       <c r="R20" t="n">
-        <v>6420328</v>
+        <v>6420287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516863</v>
+        <v>121516764</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599414</v>
+        <v>599466</v>
       </c>
       <c r="R21" t="n">
-        <v>6420330</v>
+        <v>6420338</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516966</v>
+        <v>121517133</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599406</v>
+        <v>599443</v>
       </c>
       <c r="R22" t="n">
-        <v>6420301</v>
+        <v>6420311</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516831</v>
+        <v>121516827</v>
       </c>
       <c r="B23" t="n">
         <v>98105</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599418</v>
+        <v>599429</v>
       </c>
       <c r="R23" t="n">
-        <v>6420345</v>
+        <v>6420340</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516764</v>
+        <v>121516742</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599466</v>
+        <v>599475</v>
       </c>
       <c r="R24" t="n">
-        <v>6420338</v>
+        <v>6420348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516742</v>
+        <v>121516994</v>
       </c>
       <c r="B25" t="n">
         <v>98105</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599475</v>
+        <v>599405</v>
       </c>
       <c r="R25" t="n">
-        <v>6420348</v>
+        <v>6420283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516957</v>
+        <v>121516882</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599402</v>
+        <v>599377</v>
       </c>
       <c r="R26" t="n">
-        <v>6420310</v>
+        <v>6420328</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516728</v>
+        <v>121516979</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599464</v>
+        <v>599401</v>
       </c>
       <c r="R27" t="n">
-        <v>6420340</v>
+        <v>6420297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516979</v>
+        <v>121517061</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599401</v>
+        <v>599413</v>
       </c>
       <c r="R28" t="n">
-        <v>6420297</v>
+        <v>6420284</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516931</v>
+        <v>121516742</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599381</v>
+        <v>599475</v>
       </c>
       <c r="R2" t="n">
-        <v>6420315</v>
+        <v>6420348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516848</v>
+        <v>121516863</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599420</v>
+        <v>599414</v>
       </c>
       <c r="R3" t="n">
-        <v>6420328</v>
+        <v>6420330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516780</v>
+        <v>121516728</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599458</v>
+        <v>599464</v>
       </c>
       <c r="R4" t="n">
-        <v>6420335</v>
+        <v>6420340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516920</v>
+        <v>121517008</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599374</v>
+        <v>599395</v>
       </c>
       <c r="R5" t="n">
-        <v>6420319</v>
+        <v>6420287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516837</v>
+        <v>121516957</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599422</v>
+        <v>599402</v>
       </c>
       <c r="R7" t="n">
-        <v>6420332</v>
+        <v>6420310</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516957</v>
+        <v>121516814</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599402</v>
+        <v>599427</v>
       </c>
       <c r="R8" t="n">
-        <v>6420310</v>
+        <v>6420342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516898</v>
+        <v>121516979</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599381</v>
+        <v>599401</v>
       </c>
       <c r="R9" t="n">
-        <v>6420310</v>
+        <v>6420297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516803</v>
+        <v>121516848</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599436</v>
+        <v>599420</v>
       </c>
       <c r="R10" t="n">
-        <v>6420347</v>
+        <v>6420328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516831</v>
+        <v>121517109</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,35 +1686,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1722,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599418</v>
+        <v>599411</v>
       </c>
       <c r="R11" t="n">
-        <v>6420345</v>
+        <v>6420307</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,7 +1770,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1785,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516728</v>
+        <v>121516831</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599464</v>
+        <v>599418</v>
       </c>
       <c r="R12" t="n">
-        <v>6420340</v>
+        <v>6420345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516947</v>
+        <v>121516780</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599400</v>
+        <v>599458</v>
       </c>
       <c r="R13" t="n">
-        <v>6420311</v>
+        <v>6420335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516814</v>
+        <v>121516947</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2055,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599427</v>
+        <v>599400</v>
       </c>
       <c r="R14" t="n">
-        <v>6420342</v>
+        <v>6420311</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121517109</v>
+        <v>121516931</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,39 +2133,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2170,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599411</v>
+        <v>599381</v>
       </c>
       <c r="R15" t="n">
-        <v>6420307</v>
+        <v>6420315</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,6 +2213,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516791</v>
+        <v>121516994</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599443</v>
+        <v>599405</v>
       </c>
       <c r="R16" t="n">
-        <v>6420348</v>
+        <v>6420283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516966</v>
+        <v>121516882</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599406</v>
+        <v>599377</v>
       </c>
       <c r="R18" t="n">
-        <v>6420301</v>
+        <v>6420328</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516863</v>
+        <v>121516764</v>
       </c>
       <c r="B19" t="n">
         <v>98105</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599414</v>
+        <v>599466</v>
       </c>
       <c r="R19" t="n">
-        <v>6420330</v>
+        <v>6420338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121517008</v>
+        <v>121516791</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599395</v>
+        <v>599443</v>
       </c>
       <c r="R20" t="n">
-        <v>6420287</v>
+        <v>6420348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516764</v>
+        <v>121516920</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599466</v>
+        <v>599374</v>
       </c>
       <c r="R21" t="n">
-        <v>6420338</v>
+        <v>6420319</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121517133</v>
+        <v>121516803</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599443</v>
+        <v>599436</v>
       </c>
       <c r="R22" t="n">
-        <v>6420311</v>
+        <v>6420347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516827</v>
+        <v>121517133</v>
       </c>
       <c r="B23" t="n">
         <v>98105</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599429</v>
+        <v>599443</v>
       </c>
       <c r="R23" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516742</v>
+        <v>121516837</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599475</v>
+        <v>599422</v>
       </c>
       <c r="R24" t="n">
-        <v>6420348</v>
+        <v>6420332</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516994</v>
+        <v>121517061</v>
       </c>
       <c r="B25" t="n">
         <v>98105</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599405</v>
+        <v>599413</v>
       </c>
       <c r="R25" t="n">
-        <v>6420283</v>
+        <v>6420284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516882</v>
+        <v>121516898</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599377</v>
+        <v>599381</v>
       </c>
       <c r="R26" t="n">
-        <v>6420328</v>
+        <v>6420310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516979</v>
+        <v>121516966</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599401</v>
+        <v>599406</v>
       </c>
       <c r="R27" t="n">
-        <v>6420297</v>
+        <v>6420301</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121517061</v>
+        <v>121516827</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599413</v>
+        <v>599429</v>
       </c>
       <c r="R28" t="n">
-        <v>6420284</v>
+        <v>6420340</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516742</v>
+        <v>121516863</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599475</v>
+        <v>599414</v>
       </c>
       <c r="R2" t="n">
-        <v>6420348</v>
+        <v>6420330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516863</v>
+        <v>121516848</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599414</v>
+        <v>599420</v>
       </c>
       <c r="R3" t="n">
-        <v>6420330</v>
+        <v>6420328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516728</v>
+        <v>121516947</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599464</v>
+        <v>599400</v>
       </c>
       <c r="R4" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121517008</v>
+        <v>121516831</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599395</v>
+        <v>599418</v>
       </c>
       <c r="R5" t="n">
-        <v>6420287</v>
+        <v>6420345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516747</v>
+        <v>121516931</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599464</v>
+        <v>599381</v>
       </c>
       <c r="R6" t="n">
-        <v>6420338</v>
+        <v>6420315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516957</v>
+        <v>121517061</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599402</v>
+        <v>599413</v>
       </c>
       <c r="R7" t="n">
-        <v>6420310</v>
+        <v>6420284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516814</v>
+        <v>121516742</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599427</v>
+        <v>599475</v>
       </c>
       <c r="R8" t="n">
-        <v>6420342</v>
+        <v>6420348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516979</v>
+        <v>121516803</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599401</v>
+        <v>599436</v>
       </c>
       <c r="R9" t="n">
-        <v>6420297</v>
+        <v>6420347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516848</v>
+        <v>121516882</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599420</v>
+        <v>599377</v>
       </c>
       <c r="R10" t="n">
         <v>6420328</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121517109</v>
+        <v>121516957</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,39 +1686,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1722,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599411</v>
+        <v>599402</v>
       </c>
       <c r="R11" t="n">
-        <v>6420307</v>
+        <v>6420310</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516831</v>
+        <v>121517008</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599418</v>
+        <v>599395</v>
       </c>
       <c r="R12" t="n">
-        <v>6420345</v>
+        <v>6420287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516780</v>
+        <v>121517133</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599458</v>
+        <v>599443</v>
       </c>
       <c r="R13" t="n">
-        <v>6420335</v>
+        <v>6420311</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516947</v>
+        <v>121516814</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2058,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599400</v>
+        <v>599427</v>
       </c>
       <c r="R14" t="n">
-        <v>6420311</v>
+        <v>6420342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516931</v>
+        <v>121516827</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2169,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599381</v>
+        <v>599429</v>
       </c>
       <c r="R15" t="n">
-        <v>6420315</v>
+        <v>6420340</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516994</v>
+        <v>121516920</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2280,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599405</v>
+        <v>599374</v>
       </c>
       <c r="R16" t="n">
-        <v>6420283</v>
+        <v>6420319</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121517033</v>
+        <v>121516898</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2391,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599403</v>
+        <v>599381</v>
       </c>
       <c r="R17" t="n">
-        <v>6420283</v>
+        <v>6420310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516882</v>
+        <v>121516747</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2502,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599377</v>
+        <v>599464</v>
       </c>
       <c r="R18" t="n">
-        <v>6420328</v>
+        <v>6420338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516764</v>
+        <v>121516966</v>
       </c>
       <c r="B19" t="n">
         <v>98105</v>
@@ -2613,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599466</v>
+        <v>599406</v>
       </c>
       <c r="R19" t="n">
-        <v>6420338</v>
+        <v>6420301</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516791</v>
+        <v>121516994</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2724,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599443</v>
+        <v>599405</v>
       </c>
       <c r="R20" t="n">
-        <v>6420348</v>
+        <v>6420283</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516920</v>
+        <v>121517033</v>
       </c>
       <c r="B21" t="n">
         <v>98105</v>
@@ -2835,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599374</v>
+        <v>599403</v>
       </c>
       <c r="R21" t="n">
-        <v>6420319</v>
+        <v>6420283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516803</v>
+        <v>121516764</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2946,10 +2943,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599436</v>
+        <v>599466</v>
       </c>
       <c r="R22" t="n">
-        <v>6420347</v>
+        <v>6420338</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121517133</v>
+        <v>121516979</v>
       </c>
       <c r="B23" t="n">
         <v>98105</v>
@@ -3057,10 +3054,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599443</v>
+        <v>599401</v>
       </c>
       <c r="R23" t="n">
-        <v>6420311</v>
+        <v>6420297</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516837</v>
+        <v>121516791</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -3168,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599422</v>
+        <v>599443</v>
       </c>
       <c r="R24" t="n">
-        <v>6420332</v>
+        <v>6420348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3228,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517061</v>
+        <v>121516837</v>
       </c>
       <c r="B25" t="n">
         <v>98105</v>
@@ -3279,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599413</v>
+        <v>599422</v>
       </c>
       <c r="R25" t="n">
-        <v>6420284</v>
+        <v>6420332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516898</v>
+        <v>121516728</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3390,10 +3387,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599381</v>
+        <v>599464</v>
       </c>
       <c r="R26" t="n">
-        <v>6420310</v>
+        <v>6420340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516966</v>
+        <v>121517109</v>
       </c>
       <c r="B27" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,35 +3462,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3501,13 +3502,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599406</v>
+        <v>599411</v>
       </c>
       <c r="R27" t="n">
-        <v>6420301</v>
+        <v>6420307</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3545,7 +3546,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516827</v>
+        <v>121516780</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599429</v>
+        <v>599458</v>
       </c>
       <c r="R28" t="n">
-        <v>6420340</v>
+        <v>6420335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516863</v>
+        <v>121517109</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599414</v>
+        <v>599411</v>
       </c>
       <c r="R2" t="n">
-        <v>6420330</v>
+        <v>6420307</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516848</v>
+        <v>121517061</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599420</v>
+        <v>599413</v>
       </c>
       <c r="R3" t="n">
-        <v>6420328</v>
+        <v>6420284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516947</v>
+        <v>121517133</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +948,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599400</v>
+        <v>599443</v>
       </c>
       <c r="R4" t="n">
         <v>6420311</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516831</v>
+        <v>121516728</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599418</v>
+        <v>599464</v>
       </c>
       <c r="R5" t="n">
-        <v>6420345</v>
+        <v>6420340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516931</v>
+        <v>121516966</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599381</v>
+        <v>599406</v>
       </c>
       <c r="R6" t="n">
-        <v>6420315</v>
+        <v>6420301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121517061</v>
+        <v>121516994</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599413</v>
+        <v>599405</v>
       </c>
       <c r="R7" t="n">
-        <v>6420284</v>
+        <v>6420283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516742</v>
+        <v>121516814</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599475</v>
+        <v>599427</v>
       </c>
       <c r="R8" t="n">
-        <v>6420348</v>
+        <v>6420342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516803</v>
+        <v>121516747</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599436</v>
+        <v>599464</v>
       </c>
       <c r="R9" t="n">
-        <v>6420347</v>
+        <v>6420338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516882</v>
+        <v>121516863</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599377</v>
+        <v>599414</v>
       </c>
       <c r="R10" t="n">
-        <v>6420328</v>
+        <v>6420330</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516957</v>
+        <v>121516882</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599402</v>
+        <v>599377</v>
       </c>
       <c r="R11" t="n">
-        <v>6420310</v>
+        <v>6420328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121517008</v>
+        <v>121516947</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599395</v>
+        <v>599400</v>
       </c>
       <c r="R12" t="n">
-        <v>6420287</v>
+        <v>6420311</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121517133</v>
+        <v>121516780</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599443</v>
+        <v>599458</v>
       </c>
       <c r="R13" t="n">
-        <v>6420311</v>
+        <v>6420335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516814</v>
+        <v>121516837</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599427</v>
+        <v>599422</v>
       </c>
       <c r="R14" t="n">
-        <v>6420342</v>
+        <v>6420332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516827</v>
+        <v>121516742</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599429</v>
+        <v>599475</v>
       </c>
       <c r="R15" t="n">
-        <v>6420340</v>
+        <v>6420348</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516920</v>
+        <v>121516898</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599374</v>
+        <v>599381</v>
       </c>
       <c r="R16" t="n">
-        <v>6420319</v>
+        <v>6420310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516898</v>
+        <v>121517008</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599381</v>
+        <v>599395</v>
       </c>
       <c r="R17" t="n">
-        <v>6420310</v>
+        <v>6420287</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516747</v>
+        <v>121516920</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599464</v>
+        <v>599374</v>
       </c>
       <c r="R18" t="n">
-        <v>6420338</v>
+        <v>6420319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516966</v>
+        <v>121516831</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599406</v>
+        <v>599418</v>
       </c>
       <c r="R19" t="n">
-        <v>6420301</v>
+        <v>6420345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516994</v>
+        <v>121516931</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599405</v>
+        <v>599381</v>
       </c>
       <c r="R20" t="n">
-        <v>6420283</v>
+        <v>6420315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121517033</v>
+        <v>121516957</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599403</v>
+        <v>599402</v>
       </c>
       <c r="R21" t="n">
-        <v>6420283</v>
+        <v>6420310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516764</v>
+        <v>121516827</v>
       </c>
       <c r="B22" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599466</v>
+        <v>599429</v>
       </c>
       <c r="R22" t="n">
-        <v>6420338</v>
+        <v>6420340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516979</v>
+        <v>121517033</v>
       </c>
       <c r="B23" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599401</v>
+        <v>599403</v>
       </c>
       <c r="R23" t="n">
-        <v>6420297</v>
+        <v>6420283</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516791</v>
+        <v>121516803</v>
       </c>
       <c r="B24" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599443</v>
+        <v>599436</v>
       </c>
       <c r="R24" t="n">
-        <v>6420348</v>
+        <v>6420347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516837</v>
+        <v>121516764</v>
       </c>
       <c r="B25" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599422</v>
+        <v>599466</v>
       </c>
       <c r="R25" t="n">
-        <v>6420332</v>
+        <v>6420338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3339,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516728</v>
+        <v>121516979</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599464</v>
+        <v>599401</v>
       </c>
       <c r="R26" t="n">
-        <v>6420340</v>
+        <v>6420297</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121517109</v>
+        <v>121516791</v>
       </c>
       <c r="B27" t="n">
-        <v>57509</v>
+        <v>98113</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3462,39 +3465,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3502,13 +3501,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599411</v>
+        <v>599443</v>
       </c>
       <c r="R27" t="n">
-        <v>6420307</v>
+        <v>6420348</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3546,6 +3545,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516780</v>
+        <v>121516848</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599458</v>
+        <v>599420</v>
       </c>
       <c r="R28" t="n">
-        <v>6420335</v>
+        <v>6420328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516803</v>
+        <v>121516979</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599436</v>
+        <v>599401</v>
       </c>
       <c r="R2" t="n">
-        <v>6420347</v>
+        <v>6420297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516898</v>
+        <v>121516791</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599381</v>
+        <v>599443</v>
       </c>
       <c r="R3" t="n">
-        <v>6420310</v>
+        <v>6420348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516848</v>
+        <v>121516966</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599420</v>
+        <v>599406</v>
       </c>
       <c r="R4" t="n">
-        <v>6420328</v>
+        <v>6420301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516780</v>
+        <v>121516882</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599458</v>
+        <v>599377</v>
       </c>
       <c r="R5" t="n">
-        <v>6420335</v>
+        <v>6420328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121517133</v>
+        <v>121516957</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599443</v>
+        <v>599402</v>
       </c>
       <c r="R6" t="n">
-        <v>6420311</v>
+        <v>6420310</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516994</v>
+        <v>121516837</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599405</v>
+        <v>599422</v>
       </c>
       <c r="R7" t="n">
-        <v>6420283</v>
+        <v>6420332</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516747</v>
+        <v>121517061</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599464</v>
+        <v>599413</v>
       </c>
       <c r="R8" t="n">
-        <v>6420338</v>
+        <v>6420284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516957</v>
+        <v>121516848</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599402</v>
+        <v>599420</v>
       </c>
       <c r="R9" t="n">
-        <v>6420310</v>
+        <v>6420328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121517109</v>
+        <v>121516827</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,39 +1575,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1615,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599411</v>
+        <v>599429</v>
       </c>
       <c r="R10" t="n">
-        <v>6420307</v>
+        <v>6420340</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,6 +1655,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516728</v>
+        <v>121516920</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599464</v>
+        <v>599374</v>
       </c>
       <c r="R11" t="n">
-        <v>6420340</v>
+        <v>6420319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516742</v>
+        <v>121517008</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599475</v>
+        <v>599395</v>
       </c>
       <c r="R13" t="n">
-        <v>6420348</v>
+        <v>6420287</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516791</v>
+        <v>121516764</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2058,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599443</v>
+        <v>599466</v>
       </c>
       <c r="R14" t="n">
-        <v>6420348</v>
+        <v>6420338</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516827</v>
+        <v>121516947</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2169,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599429</v>
+        <v>599400</v>
       </c>
       <c r="R15" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516863</v>
+        <v>121517033</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2280,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599414</v>
+        <v>599403</v>
       </c>
       <c r="R16" t="n">
-        <v>6420330</v>
+        <v>6420283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516979</v>
+        <v>121516831</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2391,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599401</v>
+        <v>599418</v>
       </c>
       <c r="R17" t="n">
-        <v>6420297</v>
+        <v>6420345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121517061</v>
+        <v>121516994</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2502,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599413</v>
+        <v>599405</v>
       </c>
       <c r="R18" t="n">
-        <v>6420284</v>
+        <v>6420283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516931</v>
+        <v>121516747</v>
       </c>
       <c r="B19" t="n">
         <v>98113</v>
@@ -2613,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599381</v>
+        <v>599464</v>
       </c>
       <c r="R19" t="n">
-        <v>6420315</v>
+        <v>6420338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121517008</v>
+        <v>121516863</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2724,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599395</v>
+        <v>599414</v>
       </c>
       <c r="R20" t="n">
-        <v>6420287</v>
+        <v>6420330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121517033</v>
+        <v>121516898</v>
       </c>
       <c r="B21" t="n">
         <v>98113</v>
@@ -2835,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599403</v>
+        <v>599381</v>
       </c>
       <c r="R21" t="n">
-        <v>6420283</v>
+        <v>6420310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516882</v>
+        <v>121516728</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2946,10 +2943,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599377</v>
+        <v>599464</v>
       </c>
       <c r="R22" t="n">
-        <v>6420328</v>
+        <v>6420340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516831</v>
+        <v>121516803</v>
       </c>
       <c r="B23" t="n">
         <v>98113</v>
@@ -3057,10 +3054,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599418</v>
+        <v>599436</v>
       </c>
       <c r="R23" t="n">
-        <v>6420345</v>
+        <v>6420347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516947</v>
+        <v>121516931</v>
       </c>
       <c r="B24" t="n">
         <v>98113</v>
@@ -3168,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599400</v>
+        <v>599381</v>
       </c>
       <c r="R24" t="n">
-        <v>6420311</v>
+        <v>6420315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516966</v>
+        <v>121517109</v>
       </c>
       <c r="B25" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,35 +3240,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3279,13 +3280,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599406</v>
+        <v>599411</v>
       </c>
       <c r="R25" t="n">
-        <v>6420301</v>
+        <v>6420307</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3323,7 +3324,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516837</v>
+        <v>121517133</v>
       </c>
       <c r="B26" t="n">
         <v>98113</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599422</v>
+        <v>599443</v>
       </c>
       <c r="R26" t="n">
-        <v>6420332</v>
+        <v>6420311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516764</v>
+        <v>121516780</v>
       </c>
       <c r="B27" t="n">
         <v>98113</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599466</v>
+        <v>599458</v>
       </c>
       <c r="R27" t="n">
-        <v>6420338</v>
+        <v>6420335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516920</v>
+        <v>121516742</v>
       </c>
       <c r="B28" t="n">
         <v>98113</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599374</v>
+        <v>599475</v>
       </c>
       <c r="R28" t="n">
-        <v>6420319</v>
+        <v>6420348</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516979</v>
+        <v>121516898</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599401</v>
+        <v>599381</v>
       </c>
       <c r="R2" t="n">
-        <v>6420297</v>
+        <v>6420310</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516966</v>
+        <v>121516920</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599406</v>
+        <v>599374</v>
       </c>
       <c r="R4" t="n">
-        <v>6420301</v>
+        <v>6420319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516882</v>
+        <v>121516947</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599377</v>
+        <v>599400</v>
       </c>
       <c r="R5" t="n">
-        <v>6420328</v>
+        <v>6420311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516957</v>
+        <v>121516979</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599402</v>
+        <v>599401</v>
       </c>
       <c r="R6" t="n">
-        <v>6420310</v>
+        <v>6420297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121517061</v>
+        <v>121516863</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599413</v>
+        <v>599414</v>
       </c>
       <c r="R8" t="n">
-        <v>6420284</v>
+        <v>6420330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516848</v>
+        <v>121516966</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599420</v>
+        <v>599406</v>
       </c>
       <c r="R9" t="n">
-        <v>6420328</v>
+        <v>6420301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516920</v>
+        <v>121516803</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599374</v>
+        <v>599436</v>
       </c>
       <c r="R11" t="n">
-        <v>6420319</v>
+        <v>6420347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516814</v>
+        <v>121517033</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599427</v>
+        <v>599403</v>
       </c>
       <c r="R12" t="n">
-        <v>6420342</v>
+        <v>6420283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121517008</v>
+        <v>121516994</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599395</v>
+        <v>599405</v>
       </c>
       <c r="R13" t="n">
-        <v>6420287</v>
+        <v>6420283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516764</v>
+        <v>121516747</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599466</v>
+        <v>599464</v>
       </c>
       <c r="R14" t="n">
         <v>6420338</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516947</v>
+        <v>121516780</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599400</v>
+        <v>599458</v>
       </c>
       <c r="R15" t="n">
-        <v>6420311</v>
+        <v>6420335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121517033</v>
+        <v>121516764</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599403</v>
+        <v>599466</v>
       </c>
       <c r="R16" t="n">
-        <v>6420283</v>
+        <v>6420338</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516831</v>
+        <v>121516931</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599418</v>
+        <v>599381</v>
       </c>
       <c r="R17" t="n">
-        <v>6420345</v>
+        <v>6420315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516994</v>
+        <v>121516882</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599405</v>
+        <v>599377</v>
       </c>
       <c r="R18" t="n">
-        <v>6420283</v>
+        <v>6420328</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516747</v>
+        <v>121516957</v>
       </c>
       <c r="B19" t="n">
         <v>98113</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599464</v>
+        <v>599402</v>
       </c>
       <c r="R19" t="n">
-        <v>6420338</v>
+        <v>6420310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516863</v>
+        <v>121516831</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599414</v>
+        <v>599418</v>
       </c>
       <c r="R20" t="n">
-        <v>6420330</v>
+        <v>6420345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516898</v>
+        <v>121517109</v>
       </c>
       <c r="B21" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,35 +2796,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2832,13 +2836,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599381</v>
+        <v>599411</v>
       </c>
       <c r="R21" t="n">
-        <v>6420310</v>
+        <v>6420307</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2876,7 +2880,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2895,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516728</v>
+        <v>121517008</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2943,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599464</v>
+        <v>599395</v>
       </c>
       <c r="R22" t="n">
-        <v>6420340</v>
+        <v>6420287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516803</v>
+        <v>121516814</v>
       </c>
       <c r="B23" t="n">
         <v>98113</v>
@@ -3054,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599436</v>
+        <v>599427</v>
       </c>
       <c r="R23" t="n">
-        <v>6420347</v>
+        <v>6420342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516931</v>
+        <v>121516848</v>
       </c>
       <c r="B24" t="n">
         <v>98113</v>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599381</v>
+        <v>599420</v>
       </c>
       <c r="R24" t="n">
-        <v>6420315</v>
+        <v>6420328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517109</v>
+        <v>121517061</v>
       </c>
       <c r="B25" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3240,39 +3243,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3280,13 +3279,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599411</v>
+        <v>599413</v>
       </c>
       <c r="R25" t="n">
-        <v>6420307</v>
+        <v>6420284</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,6 +3323,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121517133</v>
+        <v>121516728</v>
       </c>
       <c r="B26" t="n">
         <v>98113</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599443</v>
+        <v>599464</v>
       </c>
       <c r="R26" t="n">
-        <v>6420311</v>
+        <v>6420340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516780</v>
+        <v>121516742</v>
       </c>
       <c r="B27" t="n">
         <v>98113</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599458</v>
+        <v>599475</v>
       </c>
       <c r="R27" t="n">
-        <v>6420335</v>
+        <v>6420348</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516742</v>
+        <v>121517133</v>
       </c>
       <c r="B28" t="n">
         <v>98113</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599475</v>
+        <v>599443</v>
       </c>
       <c r="R28" t="n">
-        <v>6420348</v>
+        <v>6420311</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516898</v>
+        <v>121517061</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599381</v>
+        <v>599413</v>
       </c>
       <c r="R2" t="n">
-        <v>6420310</v>
+        <v>6420284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516791</v>
+        <v>121516920</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599443</v>
+        <v>599374</v>
       </c>
       <c r="R3" t="n">
-        <v>6420348</v>
+        <v>6420319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516920</v>
+        <v>121516764</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599374</v>
+        <v>599466</v>
       </c>
       <c r="R4" t="n">
-        <v>6420319</v>
+        <v>6420338</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516947</v>
+        <v>121516931</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599400</v>
+        <v>599381</v>
       </c>
       <c r="R5" t="n">
-        <v>6420311</v>
+        <v>6420315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516979</v>
+        <v>121516966</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599401</v>
+        <v>599406</v>
       </c>
       <c r="R6" t="n">
-        <v>6420297</v>
+        <v>6420301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516837</v>
+        <v>121516898</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599422</v>
+        <v>599381</v>
       </c>
       <c r="R7" t="n">
-        <v>6420332</v>
+        <v>6420310</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516863</v>
+        <v>121516747</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599414</v>
+        <v>599464</v>
       </c>
       <c r="R8" t="n">
-        <v>6420330</v>
+        <v>6420338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516966</v>
+        <v>121516814</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599406</v>
+        <v>599427</v>
       </c>
       <c r="R9" t="n">
-        <v>6420301</v>
+        <v>6420342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516827</v>
+        <v>121516994</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599429</v>
+        <v>599405</v>
       </c>
       <c r="R10" t="n">
-        <v>6420340</v>
+        <v>6420283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516803</v>
+        <v>121516848</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599436</v>
+        <v>599420</v>
       </c>
       <c r="R11" t="n">
-        <v>6420347</v>
+        <v>6420328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121517033</v>
+        <v>121516957</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599403</v>
+        <v>599402</v>
       </c>
       <c r="R12" t="n">
-        <v>6420283</v>
+        <v>6420310</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121516994</v>
+        <v>121517008</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599405</v>
+        <v>599395</v>
       </c>
       <c r="R13" t="n">
-        <v>6420283</v>
+        <v>6420287</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516747</v>
+        <v>121517033</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599464</v>
+        <v>599403</v>
       </c>
       <c r="R14" t="n">
-        <v>6420338</v>
+        <v>6420283</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516780</v>
+        <v>121516827</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599458</v>
+        <v>599429</v>
       </c>
       <c r="R15" t="n">
-        <v>6420335</v>
+        <v>6420340</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516764</v>
+        <v>121516780</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599466</v>
+        <v>599458</v>
       </c>
       <c r="R16" t="n">
-        <v>6420338</v>
+        <v>6420335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516931</v>
+        <v>121516831</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599381</v>
+        <v>599418</v>
       </c>
       <c r="R17" t="n">
-        <v>6420315</v>
+        <v>6420345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516882</v>
+        <v>121516728</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599377</v>
+        <v>599464</v>
       </c>
       <c r="R18" t="n">
-        <v>6420328</v>
+        <v>6420340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516957</v>
+        <v>121517133</v>
       </c>
       <c r="B19" t="n">
         <v>98113</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599402</v>
+        <v>599443</v>
       </c>
       <c r="R19" t="n">
-        <v>6420310</v>
+        <v>6420311</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516831</v>
+        <v>121516742</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599418</v>
+        <v>599475</v>
       </c>
       <c r="R20" t="n">
-        <v>6420345</v>
+        <v>6420348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121517109</v>
+        <v>121516791</v>
       </c>
       <c r="B21" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,39 +2796,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2836,13 +2832,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599411</v>
+        <v>599443</v>
       </c>
       <c r="R21" t="n">
-        <v>6420307</v>
+        <v>6420348</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2880,6 +2876,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121517008</v>
+        <v>121516882</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2946,10 +2943,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599395</v>
+        <v>599377</v>
       </c>
       <c r="R22" t="n">
-        <v>6420287</v>
+        <v>6420328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516814</v>
+        <v>121517109</v>
       </c>
       <c r="B23" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3021,35 +3018,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3057,13 +3058,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599427</v>
+        <v>599411</v>
       </c>
       <c r="R23" t="n">
-        <v>6420342</v>
+        <v>6420307</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,7 +3102,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516848</v>
+        <v>121516837</v>
       </c>
       <c r="B24" t="n">
         <v>98113</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599420</v>
+        <v>599422</v>
       </c>
       <c r="R24" t="n">
-        <v>6420328</v>
+        <v>6420332</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517061</v>
+        <v>121516803</v>
       </c>
       <c r="B25" t="n">
         <v>98113</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599413</v>
+        <v>599436</v>
       </c>
       <c r="R25" t="n">
-        <v>6420284</v>
+        <v>6420347</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516728</v>
+        <v>121516947</v>
       </c>
       <c r="B26" t="n">
         <v>98113</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599464</v>
+        <v>599400</v>
       </c>
       <c r="R26" t="n">
-        <v>6420340</v>
+        <v>6420311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516742</v>
+        <v>121516979</v>
       </c>
       <c r="B27" t="n">
         <v>98113</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599475</v>
+        <v>599401</v>
       </c>
       <c r="R27" t="n">
-        <v>6420348</v>
+        <v>6420297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121517133</v>
+        <v>121516863</v>
       </c>
       <c r="B28" t="n">
         <v>98113</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599443</v>
+        <v>599414</v>
       </c>
       <c r="R28" t="n">
-        <v>6420311</v>
+        <v>6420330</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121517061</v>
+        <v>121516791</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599413</v>
+        <v>599443</v>
       </c>
       <c r="R2" t="n">
-        <v>6420284</v>
+        <v>6420348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516920</v>
+        <v>121516837</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599374</v>
+        <v>599422</v>
       </c>
       <c r="R3" t="n">
-        <v>6420319</v>
+        <v>6420332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516764</v>
+        <v>121516994</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599466</v>
+        <v>599405</v>
       </c>
       <c r="R4" t="n">
-        <v>6420338</v>
+        <v>6420283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121516931</v>
+        <v>121517133</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599381</v>
+        <v>599443</v>
       </c>
       <c r="R5" t="n">
-        <v>6420315</v>
+        <v>6420311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516966</v>
+        <v>121516780</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599406</v>
+        <v>599458</v>
       </c>
       <c r="R6" t="n">
-        <v>6420301</v>
+        <v>6420335</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516898</v>
+        <v>121516957</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599381</v>
+        <v>599402</v>
       </c>
       <c r="R7" t="n">
         <v>6420310</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516747</v>
+        <v>121516764</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599464</v>
+        <v>599466</v>
       </c>
       <c r="R8" t="n">
         <v>6420338</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516814</v>
+        <v>121516827</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599427</v>
+        <v>599429</v>
       </c>
       <c r="R9" t="n">
-        <v>6420342</v>
+        <v>6420340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516994</v>
+        <v>121516920</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599405</v>
+        <v>599374</v>
       </c>
       <c r="R10" t="n">
-        <v>6420283</v>
+        <v>6420319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516848</v>
+        <v>121516979</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599420</v>
+        <v>599401</v>
       </c>
       <c r="R11" t="n">
-        <v>6420328</v>
+        <v>6420297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516957</v>
+        <v>121516898</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599402</v>
+        <v>599381</v>
       </c>
       <c r="R12" t="n">
         <v>6420310</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121517008</v>
+        <v>121517033</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599395</v>
+        <v>599403</v>
       </c>
       <c r="R13" t="n">
-        <v>6420287</v>
+        <v>6420283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121517033</v>
+        <v>121516966</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599403</v>
+        <v>599406</v>
       </c>
       <c r="R14" t="n">
-        <v>6420283</v>
+        <v>6420301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516827</v>
+        <v>121516728</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599429</v>
+        <v>599464</v>
       </c>
       <c r="R15" t="n">
         <v>6420340</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516780</v>
+        <v>121516747</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599458</v>
+        <v>599464</v>
       </c>
       <c r="R16" t="n">
-        <v>6420335</v>
+        <v>6420338</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121516831</v>
+        <v>121517061</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599418</v>
+        <v>599413</v>
       </c>
       <c r="R17" t="n">
-        <v>6420345</v>
+        <v>6420284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516728</v>
+        <v>121516742</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599464</v>
+        <v>599475</v>
       </c>
       <c r="R18" t="n">
-        <v>6420340</v>
+        <v>6420348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121517133</v>
+        <v>121516814</v>
       </c>
       <c r="B19" t="n">
         <v>98113</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599443</v>
+        <v>599427</v>
       </c>
       <c r="R19" t="n">
-        <v>6420311</v>
+        <v>6420342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516742</v>
+        <v>121516882</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599475</v>
+        <v>599377</v>
       </c>
       <c r="R20" t="n">
-        <v>6420348</v>
+        <v>6420328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516791</v>
+        <v>121516863</v>
       </c>
       <c r="B21" t="n">
         <v>98113</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599443</v>
+        <v>599414</v>
       </c>
       <c r="R21" t="n">
-        <v>6420348</v>
+        <v>6420330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516882</v>
+        <v>121516831</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599377</v>
+        <v>599418</v>
       </c>
       <c r="R22" t="n">
-        <v>6420328</v>
+        <v>6420345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121517109</v>
+        <v>121516848</v>
       </c>
       <c r="B23" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3018,39 +3018,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3058,13 +3054,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599411</v>
+        <v>599420</v>
       </c>
       <c r="R23" t="n">
-        <v>6420307</v>
+        <v>6420328</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,6 +3098,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516837</v>
+        <v>121516931</v>
       </c>
       <c r="B24" t="n">
         <v>98113</v>
@@ -3168,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599422</v>
+        <v>599381</v>
       </c>
       <c r="R24" t="n">
-        <v>6420332</v>
+        <v>6420315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3228,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516803</v>
+        <v>121516947</v>
       </c>
       <c r="B25" t="n">
         <v>98113</v>
@@ -3279,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599436</v>
+        <v>599400</v>
       </c>
       <c r="R25" t="n">
-        <v>6420347</v>
+        <v>6420311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516947</v>
+        <v>121517008</v>
       </c>
       <c r="B26" t="n">
         <v>98113</v>
@@ -3390,10 +3387,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599400</v>
+        <v>599395</v>
       </c>
       <c r="R26" t="n">
-        <v>6420311</v>
+        <v>6420287</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516979</v>
+        <v>121516803</v>
       </c>
       <c r="B27" t="n">
         <v>98113</v>
@@ -3501,10 +3498,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599401</v>
+        <v>599436</v>
       </c>
       <c r="R27" t="n">
-        <v>6420297</v>
+        <v>6420347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3561,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516863</v>
+        <v>121517109</v>
       </c>
       <c r="B28" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3576,35 +3573,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3612,13 +3613,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599414</v>
+        <v>599411</v>
       </c>
       <c r="R28" t="n">
-        <v>6420330</v>
+        <v>6420307</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3656,7 +3657,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48727-2024 artfynd.xlsx
+++ b/artfynd/A 48727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121516791</v>
+        <v>121517008</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599443</v>
+        <v>599395</v>
       </c>
       <c r="R2" t="n">
-        <v>6420348</v>
+        <v>6420287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121516837</v>
+        <v>121516791</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599422</v>
+        <v>599443</v>
       </c>
       <c r="R3" t="n">
-        <v>6420332</v>
+        <v>6420348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121516994</v>
+        <v>121516947</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599405</v>
+        <v>599400</v>
       </c>
       <c r="R4" t="n">
-        <v>6420283</v>
+        <v>6420311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121517133</v>
+        <v>121516803</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599443</v>
+        <v>599436</v>
       </c>
       <c r="R5" t="n">
-        <v>6420311</v>
+        <v>6420347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121516780</v>
+        <v>121516957</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599458</v>
+        <v>599402</v>
       </c>
       <c r="R6" t="n">
-        <v>6420335</v>
+        <v>6420310</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121516957</v>
+        <v>121517061</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599402</v>
+        <v>599413</v>
       </c>
       <c r="R7" t="n">
-        <v>6420310</v>
+        <v>6420284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121516764</v>
+        <v>121516966</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599466</v>
+        <v>599406</v>
       </c>
       <c r="R8" t="n">
-        <v>6420338</v>
+        <v>6420301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121516827</v>
+        <v>121516920</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599429</v>
+        <v>599374</v>
       </c>
       <c r="R9" t="n">
-        <v>6420340</v>
+        <v>6420319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121516920</v>
+        <v>121517109</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,35 +1575,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,13 +1615,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599374</v>
+        <v>599411</v>
       </c>
       <c r="R10" t="n">
-        <v>6420319</v>
+        <v>6420307</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,7 +1659,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121516979</v>
+        <v>121516848</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599401</v>
+        <v>599420</v>
       </c>
       <c r="R11" t="n">
-        <v>6420297</v>
+        <v>6420328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121516898</v>
+        <v>121516882</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599381</v>
+        <v>599377</v>
       </c>
       <c r="R12" t="n">
-        <v>6420310</v>
+        <v>6420328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121517033</v>
+        <v>121516931</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599403</v>
+        <v>599381</v>
       </c>
       <c r="R13" t="n">
-        <v>6420283</v>
+        <v>6420315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121516966</v>
+        <v>121516831</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2055,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599406</v>
+        <v>599418</v>
       </c>
       <c r="R14" t="n">
-        <v>6420301</v>
+        <v>6420345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121516728</v>
+        <v>121516827</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2166,7 +2169,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599464</v>
+        <v>599429</v>
       </c>
       <c r="R15" t="n">
         <v>6420340</v>
@@ -2229,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121516747</v>
+        <v>121516994</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2277,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599464</v>
+        <v>599405</v>
       </c>
       <c r="R16" t="n">
-        <v>6420338</v>
+        <v>6420283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121517061</v>
+        <v>121516814</v>
       </c>
       <c r="B17" t="n">
         <v>98113</v>
@@ -2388,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599413</v>
+        <v>599427</v>
       </c>
       <c r="R17" t="n">
-        <v>6420284</v>
+        <v>6420342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121516742</v>
+        <v>121516728</v>
       </c>
       <c r="B18" t="n">
         <v>98113</v>
@@ -2499,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599475</v>
+        <v>599464</v>
       </c>
       <c r="R18" t="n">
-        <v>6420348</v>
+        <v>6420340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121516814</v>
+        <v>121516898</v>
       </c>
       <c r="B19" t="n">
         <v>98113</v>
@@ -2610,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599427</v>
+        <v>599381</v>
       </c>
       <c r="R19" t="n">
-        <v>6420342</v>
+        <v>6420310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121516882</v>
+        <v>121516742</v>
       </c>
       <c r="B20" t="n">
         <v>98113</v>
@@ -2721,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599377</v>
+        <v>599475</v>
       </c>
       <c r="R20" t="n">
-        <v>6420328</v>
+        <v>6420348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121516863</v>
+        <v>121516780</v>
       </c>
       <c r="B21" t="n">
         <v>98113</v>
@@ -2832,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599414</v>
+        <v>599458</v>
       </c>
       <c r="R21" t="n">
-        <v>6420330</v>
+        <v>6420335</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121516831</v>
+        <v>121516979</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2943,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599418</v>
+        <v>599401</v>
       </c>
       <c r="R22" t="n">
-        <v>6420345</v>
+        <v>6420297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516848</v>
+        <v>121517133</v>
       </c>
       <c r="B23" t="n">
         <v>98113</v>
@@ -3054,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599420</v>
+        <v>599443</v>
       </c>
       <c r="R23" t="n">
-        <v>6420328</v>
+        <v>6420311</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516931</v>
+        <v>121516863</v>
       </c>
       <c r="B24" t="n">
         <v>98113</v>
@@ -3165,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599381</v>
+        <v>599414</v>
       </c>
       <c r="R24" t="n">
-        <v>6420315</v>
+        <v>6420330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516947</v>
+        <v>121516837</v>
       </c>
       <c r="B25" t="n">
         <v>98113</v>
@@ -3276,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599400</v>
+        <v>599422</v>
       </c>
       <c r="R25" t="n">
-        <v>6420311</v>
+        <v>6420332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121517008</v>
+        <v>121516764</v>
       </c>
       <c r="B26" t="n">
         <v>98113</v>
@@ -3387,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599395</v>
+        <v>599466</v>
       </c>
       <c r="R26" t="n">
-        <v>6420287</v>
+        <v>6420338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3453,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516803</v>
+        <v>121517033</v>
       </c>
       <c r="B27" t="n">
         <v>98113</v>
@@ -3498,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599436</v>
+        <v>599403</v>
       </c>
       <c r="R27" t="n">
-        <v>6420347</v>
+        <v>6420283</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121517109</v>
+        <v>121516747</v>
       </c>
       <c r="B28" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3573,39 +3576,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,13 +3612,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599411</v>
+        <v>599464</v>
       </c>
       <c r="R28" t="n">
-        <v>6420307</v>
+        <v>6420338</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3657,6 +3656,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
